--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DESERT_BIGHORN_RAM.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DESERT_BIGHORN_RAM.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -669,7 +675,8 @@
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -737,7 +744,8 @@
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -805,7 +813,8 @@
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -873,7 +882,8 @@
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -941,7 +951,8 @@
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1009,7 +1020,8 @@
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1077,7 +1089,8 @@
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
@@ -1145,7 +1158,8 @@
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -1213,7 +1227,8 @@
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1281,7 +1296,8 @@
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -1349,7 +1365,8 @@
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1416,8 +1433,13 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1485,7 +1507,8 @@
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -1553,7 +1576,8 @@
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>11.1</t>
         </is>
@@ -1621,7 +1645,8 @@
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
@@ -1689,7 +1714,8 @@
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>11.2</t>
         </is>
@@ -1757,7 +1783,8 @@
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>20.7</t>
         </is>
@@ -1825,7 +1852,8 @@
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1893,7 +1921,8 @@
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>11.7</t>
         </is>
@@ -1961,7 +1990,8 @@
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -2028,8 +2058,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2097,7 +2132,8 @@
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -2165,7 +2201,8 @@
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2233,7 +2270,8 @@
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
@@ -2301,7 +2339,8 @@
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
